--- a/src/importerExporter/test_import.xlsx
+++ b/src/importerExporter/test_import.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/946eb96594442864/Desktop/Chem_Database/Chemical-Database-Generator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/946eb96594442864/Desktop/Chem_Database/Chemical-Database-Generator/src/importerExporter/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{099EFCF0-47D8-4668-849F-1B819E3E63DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84644100-EE3F-491A-9B1F-EF74686BDFE1}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{099EFCF0-47D8-4668-849F-1B819E3E63DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{136AF216-1D1A-4009-A672-BBAF15DF5105}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{15659987-BF7F-4B99-A59F-8F34B386D675}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{15659987-BF7F-4B99-A59F-8F34B386D675}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,26 +37,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="154">
   <si>
     <t>Cabinet</t>
   </si>
   <si>
-    <t>A-1</t>
-  </si>
-  <si>
-    <t>Barium nitrate</t>
-  </si>
-  <si>
-    <t>A-2</t>
-  </si>
-  <si>
     <t>1 kg</t>
   </si>
   <si>
-    <t>A-5</t>
-  </si>
-  <si>
     <t>6-144</t>
   </si>
   <si>
@@ -75,9 +63,6 @@
     <t>6-147</t>
   </si>
   <si>
-    <t>4L</t>
-  </si>
-  <si>
     <t>2.5 L</t>
   </si>
   <si>
@@ -87,15 +72,9 @@
     <t>Flamm. Cab. (S1)</t>
   </si>
   <si>
-    <t>1 gal</t>
-  </si>
-  <si>
     <t xml:space="preserve">6-147 </t>
   </si>
   <si>
-    <t>20 L</t>
-  </si>
-  <si>
     <t>Flamm. Cab. (S3)</t>
   </si>
   <si>
@@ -111,30 +90,9 @@
     <t>CAS #</t>
   </si>
   <si>
-    <t>67-64-1</t>
-  </si>
-  <si>
-    <t>10022-31-8</t>
-  </si>
-  <si>
-    <t>71-43-2</t>
-  </si>
-  <si>
-    <t>7758-99-8</t>
-  </si>
-  <si>
-    <t>75-09-2</t>
-  </si>
-  <si>
-    <t>Cupric sulfate pentahydrate [AKA Copper (II) sulfate pentahydrate]</t>
-  </si>
-  <si>
     <t>90-15-3</t>
   </si>
   <si>
-    <t>7647-14-5</t>
-  </si>
-  <si>
     <t>Under SE Hood</t>
   </si>
   <si>
@@ -153,33 +111,9 @@
     <t>Fisher</t>
   </si>
   <si>
-    <t>EM Science</t>
-  </si>
-  <si>
-    <t>Brand Nu</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
-    <t>12.6 L</t>
-  </si>
-  <si>
-    <t>Sodium Chloride</t>
-  </si>
-  <si>
-    <t>1-napthol</t>
-  </si>
-  <si>
-    <t>acetone</t>
-  </si>
-  <si>
-    <t>benzene</t>
-  </si>
-  <si>
-    <t>Dichloromethane</t>
-  </si>
-  <si>
     <t>(-) Borneol (NFPA Class IIIA)</t>
   </si>
   <si>
@@ -331,13 +265,247 @@
   </si>
   <si>
     <t>109-65-9</t>
+  </si>
+  <si>
+    <t>1-Butanol (NFPA Class IC, Fp 95 deg F)</t>
+  </si>
+  <si>
+    <t>1-Chloro-2 methyl propane (NFPA Class IB)</t>
+  </si>
+  <si>
+    <t>1-Chloroadamantane</t>
+  </si>
+  <si>
+    <t>1-Chlorobutane, 99% (NFPA Class IB, Fp 10.4 deg F)</t>
+  </si>
+  <si>
+    <t>1-Napthol</t>
+  </si>
+  <si>
+    <t>1-Propanol (NFPA Class IB, Fp 59 degF)</t>
+  </si>
+  <si>
+    <t>2, 5 Hexanedione (see Acetonylacetone)</t>
+  </si>
+  <si>
+    <t>2,3,5 Triphenyltetrazolium chloride</t>
+  </si>
+  <si>
+    <t>2,4 Dinitrophenylhydrazine ( Flamm. Solid)</t>
+  </si>
+  <si>
+    <t>2,6-Dichloroindophenol sodium salt hydrate (AKA Sodium 2,6-dichloroindophenolate hydrate)</t>
+  </si>
+  <si>
+    <t>2-Amino-6-methoxybenzothiazole</t>
+  </si>
+  <si>
+    <t>2-Bromobutane (NFPA Class IB, Fp 69.8 deg F)</t>
+  </si>
+  <si>
+    <t>2-Butanone (AKA methyl ethyl ketone) (NFPA Class IB, Fp 19 deg F)</t>
+  </si>
+  <si>
+    <t>2-Chloro-2-methyl propane, 99% (NFPA Class IB, Fp -16.6 deg F)</t>
+  </si>
+  <si>
+    <t>2-Chlorobutane, 99+%  (NFPA Class IB, Fp 5 deg F)</t>
+  </si>
+  <si>
+    <t>2-Furaldehyde</t>
+  </si>
+  <si>
+    <t>2-Heptanone</t>
+  </si>
+  <si>
+    <t>2-Methyl cyclohexanone, 98% (Fp 118 deg F)</t>
+  </si>
+  <si>
+    <t>2-Methyl-2-butanol , 99% (AKA tert-Amyl alcohol) (NFPA Class IB Fp 68 deg F)</t>
+  </si>
+  <si>
+    <t>2-Methyl-2-butanol, 99%  (AKA tert-Amyl alcohol) (NFPA Class IB Fp 68 deg F)</t>
+  </si>
+  <si>
+    <t>2-Napthol</t>
+  </si>
+  <si>
+    <t>2-Octanone</t>
+  </si>
+  <si>
+    <t>2-Propanol (NFPA Class IB, Fp 53.6 deg F)</t>
+  </si>
+  <si>
+    <t>2-Propanol , anhydrous (NFPA Class IB, Fp 53.6 deg F)</t>
+  </si>
+  <si>
+    <t>3-Aminophthalhydrazide (AKA Luminol)</t>
+  </si>
+  <si>
+    <t>71-36-3</t>
+  </si>
+  <si>
+    <t>4 Liter</t>
+  </si>
+  <si>
+    <t>East Hood</t>
+  </si>
+  <si>
+    <t>1 Liter</t>
+  </si>
+  <si>
+    <t>400 mL</t>
+  </si>
+  <si>
+    <t>513-36-0</t>
+  </si>
+  <si>
+    <t>350 mL</t>
+  </si>
+  <si>
+    <t>Refrig.</t>
+  </si>
+  <si>
+    <t>935-56-8</t>
+  </si>
+  <si>
+    <t>25 g</t>
+  </si>
+  <si>
+    <t>15 g</t>
+  </si>
+  <si>
+    <t>109-69-3</t>
+  </si>
+  <si>
+    <t>1 L</t>
+  </si>
+  <si>
+    <t>1 lb</t>
+  </si>
+  <si>
+    <t>1/2 lb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baker </t>
+  </si>
+  <si>
+    <t>71-23-8</t>
+  </si>
+  <si>
+    <t>3.8L</t>
+  </si>
+  <si>
+    <t>3 L</t>
+  </si>
+  <si>
+    <t>Sigma</t>
+  </si>
+  <si>
+    <t>298-96-4</t>
+  </si>
+  <si>
+    <t>119-26-6</t>
+  </si>
+  <si>
+    <t>20 g</t>
+  </si>
+  <si>
+    <t>620-45-1</t>
+  </si>
+  <si>
+    <t>1 g</t>
+  </si>
+  <si>
+    <t>1747-60-0</t>
+  </si>
+  <si>
+    <t>78-76-2</t>
+  </si>
+  <si>
+    <t>78-93-3</t>
+  </si>
+  <si>
+    <t>3 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acros </t>
+  </si>
+  <si>
+    <t>507-20-0</t>
+  </si>
+  <si>
+    <t>78-86-4</t>
+  </si>
+  <si>
+    <t>250 mL</t>
+  </si>
+  <si>
+    <t>200 mL</t>
+  </si>
+  <si>
+    <t>98-01-1</t>
+  </si>
+  <si>
+    <t>1 liter</t>
+  </si>
+  <si>
+    <t>110-43-0</t>
+  </si>
+  <si>
+    <t>100 mL</t>
+  </si>
+  <si>
+    <t>115 mL</t>
+  </si>
+  <si>
+    <t>583-60-8</t>
+  </si>
+  <si>
+    <t>Flamm. Cab. (S2)</t>
+  </si>
+  <si>
+    <t>250 g</t>
+  </si>
+  <si>
+    <t>200 g</t>
+  </si>
+  <si>
+    <t>30 g</t>
+  </si>
+  <si>
+    <t>TCI</t>
+  </si>
+  <si>
+    <t>75-85-4</t>
+  </si>
+  <si>
+    <t>135-19-3</t>
+  </si>
+  <si>
+    <t>111-13-7</t>
+  </si>
+  <si>
+    <t>67-63-0</t>
+  </si>
+  <si>
+    <t>3.5 L</t>
+  </si>
+  <si>
+    <t>Flamm. Cab (S3)</t>
+  </si>
+  <si>
+    <t>521-31-3</t>
+  </si>
+  <si>
+    <t>no date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -365,12 +533,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -381,7 +543,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -439,11 +601,8 @@
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,6 +619,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -749,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA3E92E7-9107-4A29-BC51-5554F9243C4C}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.33203125" style="3" customWidth="1"/>
@@ -764,652 +927,1307 @@
   <sheetData>
     <row r="1" spans="1:8" s="3" customFormat="1" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="C1" s="7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>35</v>
+      <c r="B2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="13">
+        <v>40247</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="13">
+        <v>33513</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="13">
-        <v>41435</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="D4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="13">
+        <v>33513</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="12" t="s">
+      <c r="D5" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="13">
-        <v>42376</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>15</v>
-      </c>
       <c r="H5" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="13">
-        <v>43850</v>
+        <v>41</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="13">
-        <v>42171</v>
+        <v>41</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="13">
-        <v>44071</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="D9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="13">
-        <v>40247</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H9" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="13">
-        <v>33513</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="13">
-        <v>33513</v>
+        <v>49</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>35</v>
+        <v>49</v>
+      </c>
+      <c r="H12" s="13">
+        <v>33303</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="13">
+        <v>41064</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="13">
+        <v>39052</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="D15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="F15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="5">
+        <v>35261</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="B16" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="D16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="E16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="5">
+        <v>35830</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="10" t="s">
+      <c r="B17" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="10" t="s">
+      <c r="C17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="5">
+        <v>38609</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="5">
+        <v>44436</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="H19" s="13">
-        <v>33303</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="13">
-        <v>41064</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="H21" s="13">
-        <v>39052</v>
+      <c r="E21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H21" s="5">
+        <v>38615</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="H22" s="5">
-        <v>35261</v>
+        <v>38609</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H23" s="5">
-        <v>35830</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+        <v>38615</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" s="5">
+        <v>41435</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="E28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" s="5">
+        <v>38096</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H29" s="5">
+        <v>37716</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" s="5">
+        <v>37651</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31" s="5">
+        <v>33907</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H33" s="5">
+        <v>38056</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" s="5">
+        <v>38615</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="5">
+        <v>33526</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="5">
+        <v>38685</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H37" s="5">
+        <v>38615</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H38" s="5">
+        <v>42531</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H39" s="5">
+        <v>38056</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H40" s="5">
+        <v>40203</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H42" s="5">
+        <v>42970</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H43" s="5">
+        <v>44774</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H45" s="14">
+        <v>39022</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H46" s="5">
+        <v>39433</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H47" s="5">
+        <v>37716</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H48" s="5">
+        <v>39202</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H49" s="5">
+        <v>38219</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G24" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" s="5">
-        <v>38609</v>
+      <c r="G50" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H50" s="5">
+        <v>40920</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H51" s="5">
+        <v>32942</v>
       </c>
     </row>
   </sheetData>

--- a/src/importerExporter/test_import.xlsx
+++ b/src/importerExporter/test_import.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/946eb96594442864/Desktop/Chem_Database/Chemical-Database-Generator/src/importerExporter/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/946EB96594442864/Desktop/Chem_Database/Chemical-Database-Generator/src/importerExporter/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{099EFCF0-47D8-4668-849F-1B819E3E63DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{136AF216-1D1A-4009-A672-BBAF15DF5105}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="8_{099EFCF0-47D8-4668-849F-1B819E3E63DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E360869D-8F1A-46CB-88D4-2D33095F7BCF}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{15659987-BF7F-4B99-A59F-8F34B386D675}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{15659987-BF7F-4B99-A59F-8F34B386D675}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$H$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$H$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="330">
   <si>
     <t>Cabinet</t>
   </si>
@@ -499,13 +500,541 @@
   </si>
   <si>
     <t>no date</t>
+  </si>
+  <si>
+    <t>250g</t>
+  </si>
+  <si>
+    <t>Sigma-Aldrich</t>
+  </si>
+  <si>
+    <t>500g</t>
+  </si>
+  <si>
+    <t>50 mL</t>
+  </si>
+  <si>
+    <t>JT Baker</t>
+  </si>
+  <si>
+    <t>B-2</t>
+  </si>
+  <si>
+    <t>MCB</t>
+  </si>
+  <si>
+    <t>25g</t>
+  </si>
+  <si>
+    <t>Thermo</t>
+  </si>
+  <si>
+    <t>B-1</t>
+  </si>
+  <si>
+    <t>EM Science</t>
+  </si>
+  <si>
+    <t>Sargeant Welch</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>50-99-7</t>
+  </si>
+  <si>
+    <t>Diethyl malonate, 99+% (Fp 199.4 deg F)</t>
+  </si>
+  <si>
+    <t>105-53-3</t>
+  </si>
+  <si>
+    <t>Aesar</t>
+  </si>
+  <si>
+    <t>Erioglaucine sodium salt blue dye #1</t>
+  </si>
+  <si>
+    <t>Alfa Aesar</t>
+  </si>
+  <si>
+    <t>3844-45-9</t>
+  </si>
+  <si>
+    <t>Ethyl ether (anhydrous) [AKA Diethyl ether or Ether] (NFPA Class IA, Fp -49 deg F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macron </t>
+  </si>
+  <si>
+    <t>60-29-7</t>
+  </si>
+  <si>
+    <t>Ethylenediamine (Fp 93.2 deg F)</t>
+  </si>
+  <si>
+    <t>107-15-3</t>
+  </si>
+  <si>
+    <t>Ethylenediamine, anhydrous (Fp 93.2 deg F)</t>
+  </si>
+  <si>
+    <t>1 pint</t>
+  </si>
+  <si>
+    <t>Ethylenedinitrilo-tetracetic acid (AKA Ethylenediaminetetraacetic acid or EDTA)</t>
+  </si>
+  <si>
+    <t>60-00-4</t>
+  </si>
+  <si>
+    <t>Ferric chloride hexahydrate [AKA Iron (III) chloride hexahydrate]</t>
+  </si>
+  <si>
+    <t>10025-77-1</t>
+  </si>
+  <si>
+    <t>A-2</t>
+  </si>
+  <si>
+    <t>Wards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 oz </t>
+  </si>
+  <si>
+    <t>4 oz</t>
+  </si>
+  <si>
+    <t>Ferric chloride, anhydrous (Iron (III) chloride)</t>
+  </si>
+  <si>
+    <t>7705-08-0</t>
+  </si>
+  <si>
+    <t>Ferric sulfate hydrate</t>
+  </si>
+  <si>
+    <t>10028-22-5</t>
+  </si>
+  <si>
+    <t>Ferric sulfate, tetrahydrate</t>
+  </si>
+  <si>
+    <t>Ferrocene (flammable solid)</t>
+  </si>
+  <si>
+    <t>102-54-5</t>
+  </si>
+  <si>
+    <t>Ferrocene 99%</t>
+  </si>
+  <si>
+    <t>50g</t>
+  </si>
+  <si>
+    <t>A-3</t>
+  </si>
+  <si>
+    <t>Ferroin indicator standard</t>
+  </si>
+  <si>
+    <t>14634-91-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ferrous sulfate heptahydrate  [AKA Iron (II) sulfate heptahydrate] </t>
+  </si>
+  <si>
+    <t>7782-63-0</t>
+  </si>
+  <si>
+    <t>Ferrous sulfide [AKA Iron (II) sulfide]</t>
+  </si>
+  <si>
+    <t>1317-37-9</t>
+  </si>
+  <si>
+    <t>Ferrous sulfide lumps [AKA Iron (II) sulfide]</t>
+  </si>
+  <si>
+    <t>25 lb</t>
+  </si>
+  <si>
+    <t>Low Shelf</t>
+  </si>
+  <si>
+    <t>Ghost crystals (crosslinked polyacrylamide)</t>
+  </si>
+  <si>
+    <t>Flinn</t>
+  </si>
+  <si>
+    <t>71042-87-0</t>
+  </si>
+  <si>
+    <t>Glucose solution</t>
+  </si>
+  <si>
+    <t>Carolina</t>
+  </si>
+  <si>
+    <t>80 mL</t>
+  </si>
+  <si>
+    <t>Glycerine</t>
+  </si>
+  <si>
+    <t>VWR</t>
+  </si>
+  <si>
+    <t>56-81-5</t>
+  </si>
+  <si>
+    <t>1 Quart</t>
+  </si>
+  <si>
+    <t>1 quart</t>
+  </si>
+  <si>
+    <t>Glycerol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glycine (see Aminoacetic Acid) </t>
+  </si>
+  <si>
+    <t>Guaiacol</t>
+  </si>
+  <si>
+    <t>90-05-1</t>
+  </si>
+  <si>
+    <t>Heptaldehyde</t>
+  </si>
+  <si>
+    <t>111-71-7</t>
+  </si>
+  <si>
+    <t>Hexanes HPLC grade 98.5%</t>
+  </si>
+  <si>
+    <t>92112-69-1</t>
+  </si>
+  <si>
+    <t>Hydrazine hydrate solution (35% hydrazine)</t>
+  </si>
+  <si>
+    <t>10217-52-4</t>
+  </si>
+  <si>
+    <t>Hydrazine hydrate solution (64% hydrazine)</t>
+  </si>
+  <si>
+    <t>80 g</t>
+  </si>
+  <si>
+    <t>Hydroquinone</t>
+  </si>
+  <si>
+    <t>123-31-9</t>
+  </si>
+  <si>
+    <t>Hydroxylamine hydrochloride</t>
+  </si>
+  <si>
+    <t>5470-111</t>
+  </si>
+  <si>
+    <t>Ibuprofen</t>
+  </si>
+  <si>
+    <t>15687-27-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10g </t>
+  </si>
+  <si>
+    <t>51146-56-6</t>
+  </si>
+  <si>
+    <t>1g</t>
+  </si>
+  <si>
+    <t>Indigo</t>
+  </si>
+  <si>
+    <t>482-89-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MP Biomedicals </t>
+  </si>
+  <si>
+    <t>Indigo carmine</t>
+  </si>
+  <si>
+    <t>860-22-0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indigosulfonic acid, disodium salt (AKA Indigo Carmine) </t>
+  </si>
+  <si>
+    <t>Iodoethane</t>
+  </si>
+  <si>
+    <t>75-03-6</t>
+  </si>
+  <si>
+    <t>Iron(II) Sulfate Heptahydrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250g </t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>Iron, filings</t>
+  </si>
+  <si>
+    <t>7439-89-6</t>
+  </si>
+  <si>
+    <t>Iron, wire</t>
+  </si>
+  <si>
+    <t>1/4 lb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iso-Borneol </t>
+  </si>
+  <si>
+    <t>124-76-5</t>
+  </si>
+  <si>
+    <t>Lactic acid (85%)</t>
+  </si>
+  <si>
+    <t>50-21-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EM Science </t>
+  </si>
+  <si>
+    <t>Lead (II)acetate trihydrate</t>
+  </si>
+  <si>
+    <t>6080-56-4</t>
+  </si>
+  <si>
+    <t>Lead, sheet</t>
+  </si>
+  <si>
+    <t>7439-92-1</t>
+  </si>
+  <si>
+    <t>1 sheet</t>
+  </si>
+  <si>
+    <t>2 sheet</t>
+  </si>
+  <si>
+    <t>Lead, shot</t>
+  </si>
+  <si>
+    <t>Lithium chloride</t>
+  </si>
+  <si>
+    <t>7447-41-8</t>
+  </si>
+  <si>
+    <t>0.25 lb</t>
+  </si>
+  <si>
+    <t>Litmus powder</t>
+  </si>
+  <si>
+    <t>Cambosco Sci</t>
+  </si>
+  <si>
+    <t>1393-92-6</t>
+  </si>
+  <si>
+    <t>2 oz</t>
+  </si>
+  <si>
+    <t>US Biochemical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luminol (see 3-Aminophthalhydrazide) </t>
+  </si>
+  <si>
+    <t>Magnesium bromide hexahydrate</t>
+  </si>
+  <si>
+    <t>13446-53-2</t>
+  </si>
+  <si>
+    <t>Malachite green</t>
+  </si>
+  <si>
+    <t>2437-29-4</t>
+  </si>
+  <si>
+    <t>Maleic acid</t>
+  </si>
+  <si>
+    <t>110-16-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maleic anhydride </t>
+  </si>
+  <si>
+    <t>108-31-6</t>
+  </si>
+  <si>
+    <t>150 g</t>
+  </si>
+  <si>
+    <t>Alpha Aesar</t>
+  </si>
+  <si>
+    <t>Malonic acid</t>
+  </si>
+  <si>
+    <t>141-82-2</t>
+  </si>
+  <si>
+    <t>Manganese Chloride</t>
+  </si>
+  <si>
+    <t>n/a?</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>Manganese sulfate monohydrate</t>
+  </si>
+  <si>
+    <t>10034-96-5</t>
+  </si>
+  <si>
+    <t>Manganous chloride</t>
+  </si>
+  <si>
+    <t>7773-01-5</t>
+  </si>
+  <si>
+    <t>Martius yellow monohydrate</t>
+  </si>
+  <si>
+    <t>304655-86-5</t>
+  </si>
+  <si>
+    <t>12 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m-Cresol purple </t>
+  </si>
+  <si>
+    <t>2303-01-7</t>
+  </si>
+  <si>
+    <t>&lt;1g</t>
+  </si>
+  <si>
+    <t>Mercuric chloride</t>
+  </si>
+  <si>
+    <t>7487-94-7</t>
+  </si>
+  <si>
+    <t>16 oz</t>
+  </si>
+  <si>
+    <t>Mercuric iodide</t>
+  </si>
+  <si>
+    <t>7774-29-0</t>
+  </si>
+  <si>
+    <t>125 g</t>
+  </si>
+  <si>
+    <t>Mercuric oxide</t>
+  </si>
+  <si>
+    <t>21908-53-2</t>
+  </si>
+  <si>
+    <t>Methyl benzoate, Fp 181 deg F</t>
+  </si>
+  <si>
+    <t>93-58-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-146 </t>
+  </si>
+  <si>
+    <t>Methyl methacrylate polymer</t>
+  </si>
+  <si>
+    <t>9011-14-7</t>
+  </si>
+  <si>
+    <t>Methyl orange sodium salt</t>
+  </si>
+  <si>
+    <t>547-58-0</t>
+  </si>
+  <si>
+    <t>1/8 lb</t>
+  </si>
+  <si>
+    <t>Methyl red</t>
+  </si>
+  <si>
+    <t>Allied Chemical</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>63451-28-5</t>
+  </si>
+  <si>
+    <t>Methyl tert-butyl ether (MTBE)  (NFPA Class IB, Fp -18.4 deg F)</t>
+  </si>
+  <si>
+    <t>1634-04-4</t>
+  </si>
+  <si>
+    <t>2.5L</t>
+  </si>
+  <si>
+    <t>Methylaminophenol sulfate (para)</t>
+  </si>
+  <si>
+    <t>Kodak/Fisher</t>
+  </si>
+  <si>
+    <t>55-55-0</t>
+  </si>
+  <si>
+    <t>Molybdenum trioxide</t>
+  </si>
+  <si>
+    <t>1313-27-5</t>
+  </si>
+  <si>
+    <t>Mordant Orange 1 (see Alizarin Yellow R)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -533,6 +1062,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -557,10 +1099,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -604,9 +1147,19 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -912,6 +1465,2576 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA3E92E7-9107-4A29-BC51-5554F9243C4C}">
+  <dimension ref="A1:L93"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16" style="4" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="11" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="5">
+        <v>37716</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H3" s="5">
+        <v>41435</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>44063</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5">
+        <v>44063</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1996</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H15" s="5">
+        <v>40667</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" s="5">
+        <v>39881</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H20" s="5">
+        <v>33695</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H35" s="14">
+        <v>38749</v>
+      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H37" s="5">
+        <v>37716</v>
+      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H38" s="5">
+        <v>40245</v>
+      </c>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H39" s="5">
+        <v>34983</v>
+      </c>
+      <c r="I39" s="3"/>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H40" s="5">
+        <v>33914</v>
+      </c>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H41" s="5">
+        <v>42970</v>
+      </c>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H42" s="5">
+        <v>41432</v>
+      </c>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H43" s="5">
+        <v>33513</v>
+      </c>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H44" s="5">
+        <v>38756</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H46" s="5">
+        <v>39603</v>
+      </c>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H48" s="5">
+        <v>38615</v>
+      </c>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="H49" s="5">
+        <v>39895</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F51" s="1">
+        <v>307</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H53" s="5">
+        <v>41438</v>
+      </c>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H55" s="5">
+        <v>33133</v>
+      </c>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H58" s="5">
+        <v>39603</v>
+      </c>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H59" s="5">
+        <v>33259</v>
+      </c>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H62" s="5">
+        <v>31008</v>
+      </c>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H64" s="5">
+        <v>32860</v>
+      </c>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H65" s="5">
+        <v>33513</v>
+      </c>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H67" s="5">
+        <v>38749</v>
+      </c>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H69" s="5">
+        <v>42376</v>
+      </c>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H70" s="5">
+        <v>32942</v>
+      </c>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="H71" s="5">
+        <v>39850</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H72" s="5">
+        <v>33133</v>
+      </c>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H74" s="5">
+        <v>32907</v>
+      </c>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H81" s="5">
+        <v>41795</v>
+      </c>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+    </row>
+    <row r="89" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H89" s="5">
+        <v>43621</v>
+      </c>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+    </row>
+    <row r="90" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H92" s="5">
+        <v>33303</v>
+      </c>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+    </row>
+    <row r="93" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <printOptions gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C
+&amp;RPage  &amp;P</oddHeader>
+    <oddFooter>Prepared by Administrator &amp;D&amp;RPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14BA78B3-A6DA-43AA-87DC-EE1620157CF7}">
   <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -925,7 +4048,7 @@
     <col min="8" max="8" width="10.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="3" customFormat="1" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
@@ -2231,14 +5354,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;C
-&amp;RPage  &amp;P</oddHeader>
-    <oddFooter>Prepared by Administrator &amp;D&amp;RPage &amp;P</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>